--- a/GameConfig/Datas/情绪配置表.xlsx
+++ b/GameConfig/Datas/情绪配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="情绪配置表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情绪配置表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,7 +516,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>温柔</t>
+          <t>理解</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>好奇</t>
+          <t>喜悦</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -550,12 +550,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>克制</t>
+          <t>失落</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>#D7D3E8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>好奇</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>#D5E8D4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>E00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>无情绪</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>#E6E6E6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>珍惜</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>#FCE5CD</t>
         </is>
       </c>
     </row>

--- a/GameConfig/Datas/情绪配置表.xlsx
+++ b/GameConfig/Datas/情绪配置表.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,194 +415,205 @@
   </sheetPr>
   <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>emotionName</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>displayColor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>情绪ID</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>情绪名</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>占位颜色 #RRGGBB</t>
         </is>
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>理解</t>
+          <t>喜悦</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>#F5C6CB</t>
+          <t>#CDE7F0</t>
         </is>
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>喜悦</t>
+          <t>失落</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>#CDE7F0</t>
+          <t>#D7D3E8</t>
         </is>
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>失落</t>
+          <t>好奇</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>#D7D3E8</t>
+          <t>#D5E8D4</t>
         </is>
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>好奇</t>
+          <t>无情绪</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>#D5E8D4</t>
+          <t>#E6E6E6</t>
         </is>
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>E00</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>无情绪</t>
+          <t>怀念</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>#E6E6E6</t>
+          <t>#FCE5CD</t>
         </is>
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>珍惜</t>
+          <t>自我</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>#FCE5CD</t>
+          <t>#EDE0D4</t>
         </is>
       </c>
     </row>
